--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>name</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>profile_photo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -477,6 +482,7 @@
           <t>Admin User</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -487,10 +493,8 @@
           <t>Avinash</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -502,6 +506,83 @@
           <t>Avinash</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kiran</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Kiran</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>profile_3_PHOTO.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sarthak</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sarthak</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mahesh</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Mahesh</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,26 @@
           <t>profile_photo</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>emergency_number</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>emergency_contact_name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -483,6 +503,10 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -507,6 +531,10 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -530,9 +558,25 @@
           <t>Kiran</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>profile_3_PHOTO.jpg</t>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>kiranaglawe18@gmail.com</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>9766148444</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9766148444</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Kiran</t>
         </is>
       </c>
     </row>
@@ -559,6 +603,10 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -583,6 +631,10 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,27 +456,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>profile_photo</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
           <t>email</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>emergency_number</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>emergency_contact_name</t>
         </is>
       </c>
     </row>
@@ -489,8 +469,10 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>123</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -502,139 +484,11 @@
           <t>Admin User</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Avinash</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1234</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Avinash</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kiran</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1234</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Kiran</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>kiranaglawe18@gmail.com</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>9766148444</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>9766148444</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Kiran</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Sarthak</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1234</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Sarthak</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Mahesh</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1234</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Mahesh</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>renvoratech@gmail.com</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,10 +469,8 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="C2" t="n">
+        <v>123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -489,6 +487,56 @@
           <t>renvoratech@gmail.com</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kiran</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Kiran</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kiran</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Kiran</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,56 +487,6 @@
           <t>renvoratech@gmail.com</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Kiran</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1234</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Kiran</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kiran</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Kiran</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,58 @@
           <t>renvoratech@gmail.com</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RV001</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RV@001</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Kiran Narhari Aglawe</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RV002</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RV002</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Avinash Ganesh Chate</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
